--- a/premissas_csa.xlsx
+++ b/premissas_csa.xlsx
@@ -5,22 +5,35 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/05FE6D64DE7CBA42/Área de Trabalho/Github/saneamento_amapa/05_modelo/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\malug\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{93D2229C-FB8C-4ECE-BA67-DD1C9CC1AF95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A4539282-770A-486B-B0D0-9D06AC9C07DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="premissas" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="185">
   <si>
     <t>premissa</t>
   </si>
@@ -479,6 +492,102 @@
   </si>
   <si>
     <t>ano 18 da concessão</t>
+  </si>
+  <si>
+    <t>inadimplencia_inicial</t>
+  </si>
+  <si>
+    <t>Equatorial 2T26: provisões ÷ receita (1S26)</t>
+  </si>
+  <si>
+    <t>inadimplencia_final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ano_inadimplencia_final </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ano 15 de operação </t>
+  </si>
+  <si>
+    <t>capex_por_economia_agua</t>
+  </si>
+  <si>
+    <t>R$ por nova economia</t>
+  </si>
+  <si>
+    <t>R$ 0,8 bi ÷ 309 mil novas economias</t>
+  </si>
+  <si>
+    <t>capex_por_economia_esgoto</t>
+  </si>
+  <si>
+    <t>R$ 2,2 bi ÷ 356 mil novas economias</t>
+  </si>
+  <si>
+    <t>capex_manutencao</t>
+  </si>
+  <si>
+    <t>% da receita</t>
+  </si>
+  <si>
+    <t>capex dos anos maduros ÷ receita</t>
+  </si>
+  <si>
+    <t>populacao_2026</t>
+  </si>
+  <si>
+    <t>IBGE, estimativa populacional 2026</t>
+  </si>
+  <si>
+    <t>Soma dos 16 municípios do Amapá (toda a área da concessão)</t>
+  </si>
+  <si>
+    <t>habitantes_por_domicilio</t>
+  </si>
+  <si>
+    <t>habitantes/domicílio</t>
+  </si>
+  <si>
+    <t>Plano de Negócios Referencial BNDES</t>
+  </si>
+  <si>
+    <t>“250 litros por habitante x 3,4 habitantes por residência”</t>
+  </si>
+  <si>
+    <t>adesao_final</t>
+  </si>
+  <si>
+    <t>Meta de adesão “com base em operações privadas”, atingida no ano da universalização da água. O plano assume que o esgoto tem a mesma adesão da água</t>
+  </si>
+  <si>
+    <t>ano_adesao_final</t>
+  </si>
+  <si>
+    <t>Contrato, Anexo III (meta de cobertura de água)</t>
+  </si>
+  <si>
+    <t>Anexo III</t>
+  </si>
+  <si>
+    <t>Anexo I</t>
+  </si>
+  <si>
+    <t>Premissa própria: igual a ano_meta_agua, seguindo a lógica do plano</t>
+  </si>
+  <si>
+    <t>% da população</t>
+  </si>
+  <si>
+    <t>Concessão abrange as zonas urbanas (Plano BNDES, p. 5 e 8)</t>
+  </si>
+  <si>
+    <t>IBGE, Censo 2010, SIDRA Tabela 202</t>
+  </si>
+  <si>
+    <t>taxa_urbanizacao</t>
+  </si>
+  <si>
+    <t>habitantes</t>
   </si>
 </sst>
 </file>
@@ -517,12 +626,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -825,7 +935,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:F72"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -1973,6 +2083,212 @@
         <v>152</v>
       </c>
     </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>153</v>
+      </c>
+      <c r="B62">
+        <v>0.188</v>
+      </c>
+      <c r="C62" t="s">
+        <v>68</v>
+      </c>
+      <c r="D62" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>155</v>
+      </c>
+      <c r="B63">
+        <v>0.1</v>
+      </c>
+      <c r="C63" t="s">
+        <v>68</v>
+      </c>
+      <c r="D63" t="s">
+        <v>146</v>
+      </c>
+      <c r="E63">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>156</v>
+      </c>
+      <c r="B64" s="1">
+        <v>2037</v>
+      </c>
+      <c r="C64" t="s">
+        <v>11</v>
+      </c>
+      <c r="D64" t="s">
+        <v>146</v>
+      </c>
+      <c r="E64">
+        <v>24</v>
+      </c>
+      <c r="F64" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>158</v>
+      </c>
+      <c r="B65">
+        <v>2587</v>
+      </c>
+      <c r="C65" t="s">
+        <v>159</v>
+      </c>
+      <c r="D65" t="s">
+        <v>146</v>
+      </c>
+      <c r="E65">
+        <v>10</v>
+      </c>
+      <c r="F65" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>161</v>
+      </c>
+      <c r="B66">
+        <v>6188</v>
+      </c>
+      <c r="C66" t="s">
+        <v>159</v>
+      </c>
+      <c r="D66" t="s">
+        <v>146</v>
+      </c>
+      <c r="E66">
+        <v>10</v>
+      </c>
+      <c r="F66" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>163</v>
+      </c>
+      <c r="B67">
+        <v>0.04</v>
+      </c>
+      <c r="C67" t="s">
+        <v>164</v>
+      </c>
+      <c r="D67" t="s">
+        <v>146</v>
+      </c>
+      <c r="E67" t="s">
+        <v>178</v>
+      </c>
+      <c r="F67" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>166</v>
+      </c>
+      <c r="B68" s="3">
+        <v>809953</v>
+      </c>
+      <c r="C68" t="s">
+        <v>184</v>
+      </c>
+      <c r="D68" t="s">
+        <v>167</v>
+      </c>
+      <c r="F68" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>169</v>
+      </c>
+      <c r="B69">
+        <v>3.4</v>
+      </c>
+      <c r="C69" t="s">
+        <v>170</v>
+      </c>
+      <c r="D69" t="s">
+        <v>171</v>
+      </c>
+      <c r="E69">
+        <v>12</v>
+      </c>
+      <c r="F69" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>173</v>
+      </c>
+      <c r="B70">
+        <v>0.85</v>
+      </c>
+      <c r="C70" t="s">
+        <v>68</v>
+      </c>
+      <c r="D70" t="s">
+        <v>171</v>
+      </c>
+      <c r="E70">
+        <v>11</v>
+      </c>
+      <c r="F70" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>175</v>
+      </c>
+      <c r="B71">
+        <v>2033</v>
+      </c>
+      <c r="C71" t="s">
+        <v>11</v>
+      </c>
+      <c r="D71" t="s">
+        <v>176</v>
+      </c>
+      <c r="E71" t="s">
+        <v>177</v>
+      </c>
+      <c r="F71" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>183</v>
+      </c>
+      <c r="B72">
+        <v>0.89770000000000005</v>
+      </c>
+      <c r="C72" t="s">
+        <v>180</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s">
+        <v>181</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
